--- a/artfynd/A 2142-2019 artfynd.xlsx
+++ b/artfynd/A 2142-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1581,6 +1581,1187 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113714595</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90573</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skorped värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>642825</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7037328</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113714592</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56029</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skorped värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>642734</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7037340</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>En tupp</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113712373</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90316</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Romell) Singer</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skorped värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>642856</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7037356</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113712377</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5164</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skorped värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>642895</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7037392</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>113714598</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90149</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skorped värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>642871</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7037374</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>113712375</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90412</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>658</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skorped värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>642877</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7037381</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>113714590</v>
+      </c>
+      <c r="B16" t="n">
+        <v>77953</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skorped värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>642795</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7037307</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>113714591</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79265</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skorped värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>642802</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7037327</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>113714596</v>
+      </c>
+      <c r="B18" t="n">
+        <v>86389</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>510</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skorped värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>642839</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7037339</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>113714594</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91413</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skorped värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>642708</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7037261</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Många</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>113712369</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91406</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skorped värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>642716</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7037332</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Många</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2142-2019 artfynd.xlsx
+++ b/artfynd/A 2142-2019 artfynd.xlsx
@@ -1583,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113714595</v>
+        <v>113714601</v>
       </c>
       <c r="B10" t="n">
-        <v>90573</v>
+        <v>5164</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,25 +1595,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>642825</v>
+        <v>642895</v>
       </c>
       <c r="R10" t="n">
-        <v>7037328</v>
+        <v>7037392</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1689,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113714592</v>
+        <v>113712375</v>
       </c>
       <c r="B11" t="n">
-        <v>56029</v>
+        <v>90412</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,25 +1701,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>642734</v>
+        <v>642877</v>
       </c>
       <c r="R11" t="n">
-        <v>7037340</v>
+        <v>7037381</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,11 +1765,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-10-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>En tupp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712373</v>
+        <v>113712371</v>
       </c>
       <c r="B12" t="n">
-        <v>90316</v>
+        <v>90573</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>642856</v>
+        <v>642825</v>
       </c>
       <c r="R12" t="n">
-        <v>7037356</v>
+        <v>7037328</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1906,10 +1901,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113712377</v>
+        <v>113712367</v>
       </c>
       <c r="B13" t="n">
-        <v>5164</v>
+        <v>79265</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,25 +1913,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1946,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>642895</v>
+        <v>642802</v>
       </c>
       <c r="R13" t="n">
-        <v>7037392</v>
+        <v>7037327</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2012,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113714598</v>
+        <v>113714592</v>
       </c>
       <c r="B14" t="n">
-        <v>90149</v>
+        <v>56029</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2024,25 +2019,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2052,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>642871</v>
+        <v>642734</v>
       </c>
       <c r="R14" t="n">
-        <v>7037374</v>
+        <v>7037340</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2088,6 +2083,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113712375</v>
+        <v>113714597</v>
       </c>
       <c r="B15" t="n">
-        <v>90412</v>
+        <v>90316</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,25 +2130,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>642877</v>
+        <v>642856</v>
       </c>
       <c r="R15" t="n">
-        <v>7037381</v>
+        <v>7037356</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2224,10 +2224,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113714590</v>
+        <v>113712374</v>
       </c>
       <c r="B16" t="n">
-        <v>77953</v>
+        <v>90149</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,21 +2240,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>642795</v>
+        <v>642871</v>
       </c>
       <c r="R16" t="n">
-        <v>7037307</v>
+        <v>7037374</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113714591</v>
+        <v>113712372</v>
       </c>
       <c r="B17" t="n">
-        <v>79265</v>
+        <v>86389</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2346,21 +2346,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>642802</v>
+        <v>642839</v>
       </c>
       <c r="R17" t="n">
-        <v>7037327</v>
+        <v>7037339</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113714596</v>
+        <v>113712370</v>
       </c>
       <c r="B18" t="n">
-        <v>86389</v>
+        <v>91413</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>642839</v>
+        <v>642708</v>
       </c>
       <c r="R18" t="n">
-        <v>7037339</v>
+        <v>7037261</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2512,6 +2512,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Många</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2542,10 +2547,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113714594</v>
+        <v>113714593</v>
       </c>
       <c r="B19" t="n">
-        <v>91413</v>
+        <v>91406</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2558,21 +2563,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2582,10 +2587,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>642708</v>
+        <v>642716</v>
       </c>
       <c r="R19" t="n">
-        <v>7037261</v>
+        <v>7037332</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2653,10 +2658,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113712369</v>
+        <v>113712366</v>
       </c>
       <c r="B20" t="n">
-        <v>91406</v>
+        <v>77953</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2669,21 +2674,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2693,10 +2698,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>642716</v>
+        <v>642795</v>
       </c>
       <c r="R20" t="n">
-        <v>7037332</v>
+        <v>7037307</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2729,11 +2734,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-10-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Många</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 2142-2019 artfynd.xlsx
+++ b/artfynd/A 2142-2019 artfynd.xlsx
@@ -1583,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113714601</v>
+        <v>113712372</v>
       </c>
       <c r="B10" t="n">
-        <v>5164</v>
+        <v>86390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,25 +1595,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>642895</v>
+        <v>642839</v>
       </c>
       <c r="R10" t="n">
-        <v>7037392</v>
+        <v>7037339</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1692,7 +1692,7 @@
         <v>113712375</v>
       </c>
       <c r="B11" t="n">
-        <v>90412</v>
+        <v>90416</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712371</v>
+        <v>113714597</v>
       </c>
       <c r="B12" t="n">
-        <v>90573</v>
+        <v>90320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>642825</v>
+        <v>642856</v>
       </c>
       <c r="R12" t="n">
-        <v>7037328</v>
+        <v>7037356</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1901,10 +1901,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113712367</v>
+        <v>113714593</v>
       </c>
       <c r="B13" t="n">
-        <v>79265</v>
+        <v>91410</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1917,21 +1917,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>642802</v>
+        <v>642716</v>
       </c>
       <c r="R13" t="n">
-        <v>7037327</v>
+        <v>7037332</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1977,6 +1977,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Många</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,10 +2012,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113714592</v>
+        <v>113714595</v>
       </c>
       <c r="B14" t="n">
-        <v>56029</v>
+        <v>90577</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,25 +2024,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2047,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>642734</v>
+        <v>642825</v>
       </c>
       <c r="R14" t="n">
-        <v>7037340</v>
+        <v>7037328</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2083,11 +2088,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-10-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>En tupp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113714597</v>
+        <v>113712368</v>
       </c>
       <c r="B15" t="n">
-        <v>90316</v>
+        <v>56029</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,25 +2130,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>48</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>642856</v>
+        <v>642734</v>
       </c>
       <c r="R15" t="n">
-        <v>7037356</v>
+        <v>7037340</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2194,6 +2194,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113712374</v>
+        <v>113712377</v>
       </c>
       <c r="B16" t="n">
-        <v>90149</v>
+        <v>5164</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2236,25 +2241,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>642871</v>
+        <v>642895</v>
       </c>
       <c r="R16" t="n">
-        <v>7037374</v>
+        <v>7037392</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2330,10 +2335,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113712372</v>
+        <v>113712366</v>
       </c>
       <c r="B17" t="n">
-        <v>86389</v>
+        <v>77953</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2346,21 +2351,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2370,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>642839</v>
+        <v>642795</v>
       </c>
       <c r="R17" t="n">
-        <v>7037339</v>
+        <v>7037307</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2436,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113712370</v>
+        <v>113712367</v>
       </c>
       <c r="B18" t="n">
-        <v>91413</v>
+        <v>79265</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2452,21 +2457,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2476,10 +2481,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>642708</v>
+        <v>642802</v>
       </c>
       <c r="R18" t="n">
-        <v>7037261</v>
+        <v>7037327</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2512,11 +2517,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-10-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Många</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,10 +2547,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113714593</v>
+        <v>113712374</v>
       </c>
       <c r="B19" t="n">
-        <v>91406</v>
+        <v>90153</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2563,21 +2563,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2059</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>642716</v>
+        <v>642871</v>
       </c>
       <c r="R19" t="n">
-        <v>7037332</v>
+        <v>7037374</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2623,11 +2623,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-10-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Många</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2658,10 +2653,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113712366</v>
+        <v>113712370</v>
       </c>
       <c r="B20" t="n">
-        <v>77953</v>
+        <v>91417</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2674,21 +2669,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2698,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>642795</v>
+        <v>642708</v>
       </c>
       <c r="R20" t="n">
-        <v>7037307</v>
+        <v>7037261</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2734,6 +2729,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Många</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 2142-2019 artfynd.xlsx
+++ b/artfynd/A 2142-2019 artfynd.xlsx
@@ -1583,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113712372</v>
+        <v>113712375</v>
       </c>
       <c r="B10" t="n">
-        <v>86390</v>
+        <v>90416</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,21 +1599,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>642839</v>
+        <v>642877</v>
       </c>
       <c r="R10" t="n">
-        <v>7037339</v>
+        <v>7037381</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1689,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712375</v>
+        <v>113714590</v>
       </c>
       <c r="B11" t="n">
-        <v>90416</v>
+        <v>77953</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,21 +1705,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>642877</v>
+        <v>642795</v>
       </c>
       <c r="R11" t="n">
-        <v>7037381</v>
+        <v>7037307</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113714597</v>
+        <v>113714593</v>
       </c>
       <c r="B12" t="n">
-        <v>90320</v>
+        <v>91410</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>642856</v>
+        <v>642716</v>
       </c>
       <c r="R12" t="n">
-        <v>7037356</v>
+        <v>7037332</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1871,6 +1871,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Många</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,10 +1906,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113714593</v>
+        <v>113712372</v>
       </c>
       <c r="B13" t="n">
-        <v>91410</v>
+        <v>86390</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1917,21 +1922,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1946,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>642716</v>
+        <v>642839</v>
       </c>
       <c r="R13" t="n">
-        <v>7037332</v>
+        <v>7037339</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1977,11 +1982,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-10-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Många</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,10 +2012,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113714595</v>
+        <v>113712370</v>
       </c>
       <c r="B14" t="n">
-        <v>90577</v>
+        <v>91417</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2024,25 +2024,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>642825</v>
+        <v>642708</v>
       </c>
       <c r="R14" t="n">
-        <v>7037328</v>
+        <v>7037261</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2088,6 +2088,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Många</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,10 +2123,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113712368</v>
+        <v>113714591</v>
       </c>
       <c r="B15" t="n">
-        <v>56029</v>
+        <v>79265</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,25 +2135,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>642734</v>
+        <v>642802</v>
       </c>
       <c r="R15" t="n">
-        <v>7037340</v>
+        <v>7037327</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2194,11 +2199,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-10-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>En tupp</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113712377</v>
+        <v>113714601</v>
       </c>
       <c r="B16" t="n">
         <v>5164</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113712366</v>
+        <v>113712368</v>
       </c>
       <c r="B17" t="n">
-        <v>77953</v>
+        <v>56029</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2347,25 +2347,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>642795</v>
+        <v>642734</v>
       </c>
       <c r="R17" t="n">
-        <v>7037307</v>
+        <v>7037340</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2411,6 +2411,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2441,10 +2446,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113712367</v>
+        <v>113714598</v>
       </c>
       <c r="B18" t="n">
-        <v>79265</v>
+        <v>90153</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2457,21 +2462,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2481,10 +2486,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>642802</v>
+        <v>642871</v>
       </c>
       <c r="R18" t="n">
-        <v>7037327</v>
+        <v>7037374</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2547,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113712374</v>
+        <v>113712373</v>
       </c>
       <c r="B19" t="n">
-        <v>90153</v>
+        <v>90320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2559,25 +2564,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>48</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2587,10 +2592,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>642871</v>
+        <v>642856</v>
       </c>
       <c r="R19" t="n">
-        <v>7037374</v>
+        <v>7037356</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2653,10 +2658,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113712370</v>
+        <v>113714595</v>
       </c>
       <c r="B20" t="n">
-        <v>91417</v>
+        <v>90577</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2665,25 +2670,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2693,10 +2698,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>642708</v>
+        <v>642825</v>
       </c>
       <c r="R20" t="n">
-        <v>7037261</v>
+        <v>7037328</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2729,11 +2734,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-10-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Många</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 2142-2019 artfynd.xlsx
+++ b/artfynd/A 2142-2019 artfynd.xlsx
@@ -1583,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113712375</v>
+        <v>113712367</v>
       </c>
       <c r="B10" t="n">
-        <v>90416</v>
+        <v>79265</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,21 +1599,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>642877</v>
+        <v>642802</v>
       </c>
       <c r="R10" t="n">
-        <v>7037381</v>
+        <v>7037327</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1689,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113714590</v>
+        <v>113712374</v>
       </c>
       <c r="B11" t="n">
-        <v>77953</v>
+        <v>90153</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,21 +1705,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>642795</v>
+        <v>642871</v>
       </c>
       <c r="R11" t="n">
-        <v>7037307</v>
+        <v>7037374</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113714593</v>
+        <v>113712370</v>
       </c>
       <c r="B12" t="n">
-        <v>91410</v>
+        <v>91417</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>642716</v>
+        <v>642708</v>
       </c>
       <c r="R12" t="n">
-        <v>7037332</v>
+        <v>7037261</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113712372</v>
+        <v>113712375</v>
       </c>
       <c r="B13" t="n">
-        <v>86390</v>
+        <v>90416</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,21 +1922,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>642839</v>
+        <v>642877</v>
       </c>
       <c r="R13" t="n">
-        <v>7037339</v>
+        <v>7037381</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113712370</v>
+        <v>113714593</v>
       </c>
       <c r="B14" t="n">
-        <v>91417</v>
+        <v>91410</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2028,21 +2028,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>642708</v>
+        <v>642716</v>
       </c>
       <c r="R14" t="n">
-        <v>7037261</v>
+        <v>7037332</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113714591</v>
+        <v>113714596</v>
       </c>
       <c r="B15" t="n">
-        <v>79265</v>
+        <v>86390</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2139,21 +2139,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>642802</v>
+        <v>642839</v>
       </c>
       <c r="R15" t="n">
-        <v>7037327</v>
+        <v>7037339</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2229,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113714601</v>
+        <v>113712377</v>
       </c>
       <c r="B16" t="n">
         <v>5164</v>
@@ -2335,7 +2335,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113712368</v>
+        <v>113714592</v>
       </c>
       <c r="B17" t="n">
         <v>56029</v>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113714598</v>
+        <v>113712366</v>
       </c>
       <c r="B18" t="n">
-        <v>90153</v>
+        <v>77953</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2462,21 +2462,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>642871</v>
+        <v>642795</v>
       </c>
       <c r="R18" t="n">
-        <v>7037374</v>
+        <v>7037307</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2552,7 +2552,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113712373</v>
+        <v>113714597</v>
       </c>
       <c r="B19" t="n">
         <v>90320</v>

--- a/artfynd/A 2142-2019 artfynd.xlsx
+++ b/artfynd/A 2142-2019 artfynd.xlsx
@@ -1583,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113712367</v>
+        <v>113714601</v>
       </c>
       <c r="B10" t="n">
-        <v>79265</v>
+        <v>5164</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,25 +1595,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>642802</v>
+        <v>642895</v>
       </c>
       <c r="R10" t="n">
-        <v>7037327</v>
+        <v>7037392</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1689,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712374</v>
+        <v>113712375</v>
       </c>
       <c r="B11" t="n">
-        <v>90153</v>
+        <v>90416</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,21 +1705,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>642871</v>
+        <v>642877</v>
       </c>
       <c r="R11" t="n">
-        <v>7037374</v>
+        <v>7037381</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712370</v>
+        <v>113714590</v>
       </c>
       <c r="B12" t="n">
-        <v>91417</v>
+        <v>77953</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>642708</v>
+        <v>642795</v>
       </c>
       <c r="R12" t="n">
-        <v>7037261</v>
+        <v>7037307</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1871,11 +1871,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-10-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Många</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,10 +1901,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113712375</v>
+        <v>113712369</v>
       </c>
       <c r="B13" t="n">
-        <v>90416</v>
+        <v>91410</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,21 +1917,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1946,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>642877</v>
+        <v>642716</v>
       </c>
       <c r="R13" t="n">
-        <v>7037381</v>
+        <v>7037332</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1982,6 +1977,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Många</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,10 +2012,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113714593</v>
+        <v>113714596</v>
       </c>
       <c r="B14" t="n">
-        <v>91410</v>
+        <v>86390</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2028,21 +2028,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>642716</v>
+        <v>642839</v>
       </c>
       <c r="R14" t="n">
-        <v>7037332</v>
+        <v>7037339</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2088,11 +2088,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-10-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Många</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113714596</v>
+        <v>113714598</v>
       </c>
       <c r="B15" t="n">
-        <v>86390</v>
+        <v>90153</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2139,21 +2134,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2163,10 +2158,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>642839</v>
+        <v>642871</v>
       </c>
       <c r="R15" t="n">
-        <v>7037339</v>
+        <v>7037374</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2229,10 +2224,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113712377</v>
+        <v>113714594</v>
       </c>
       <c r="B16" t="n">
-        <v>5164</v>
+        <v>91417</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2241,25 +2236,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>642895</v>
+        <v>642708</v>
       </c>
       <c r="R16" t="n">
-        <v>7037392</v>
+        <v>7037261</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2305,6 +2300,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Många</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2335,10 +2335,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113714592</v>
+        <v>113714595</v>
       </c>
       <c r="B17" t="n">
-        <v>56029</v>
+        <v>90577</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2347,25 +2347,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>642734</v>
+        <v>642825</v>
       </c>
       <c r="R17" t="n">
-        <v>7037340</v>
+        <v>7037328</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2411,11 +2411,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-10-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>En tupp</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2446,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113712366</v>
+        <v>113714592</v>
       </c>
       <c r="B18" t="n">
-        <v>77953</v>
+        <v>56029</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2458,25 +2453,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2486,10 +2481,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>642795</v>
+        <v>642734</v>
       </c>
       <c r="R18" t="n">
-        <v>7037307</v>
+        <v>7037340</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2522,6 +2517,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113714597</v>
+        <v>113712367</v>
       </c>
       <c r="B19" t="n">
-        <v>90320</v>
+        <v>79265</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2564,25 +2564,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>642856</v>
+        <v>642802</v>
       </c>
       <c r="R19" t="n">
-        <v>7037356</v>
+        <v>7037327</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2658,10 +2658,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113714595</v>
+        <v>113712373</v>
       </c>
       <c r="B20" t="n">
-        <v>90577</v>
+        <v>90320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2674,21 +2674,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>642825</v>
+        <v>642856</v>
       </c>
       <c r="R20" t="n">
-        <v>7037328</v>
+        <v>7037356</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 2142-2019 artfynd.xlsx
+++ b/artfynd/A 2142-2019 artfynd.xlsx
@@ -1583,7 +1583,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113714601</v>
+        <v>113712377</v>
       </c>
       <c r="B10" t="n">
         <v>5164</v>
@@ -1689,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712375</v>
+        <v>113714590</v>
       </c>
       <c r="B11" t="n">
-        <v>90416</v>
+        <v>77953</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,21 +1705,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>642877</v>
+        <v>642795</v>
       </c>
       <c r="R11" t="n">
-        <v>7037381</v>
+        <v>7037307</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113714590</v>
+        <v>113714591</v>
       </c>
       <c r="B12" t="n">
-        <v>77953</v>
+        <v>79265</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>642795</v>
+        <v>642802</v>
       </c>
       <c r="R12" t="n">
-        <v>7037307</v>
+        <v>7037327</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1901,10 +1901,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113712369</v>
+        <v>113714599</v>
       </c>
       <c r="B13" t="n">
-        <v>91410</v>
+        <v>90416</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1917,21 +1917,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>642716</v>
+        <v>642877</v>
       </c>
       <c r="R13" t="n">
-        <v>7037332</v>
+        <v>7037381</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1977,11 +1977,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-10-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Många</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113714596</v>
+        <v>113714598</v>
       </c>
       <c r="B14" t="n">
-        <v>86390</v>
+        <v>90153</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2028,21 +2023,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2052,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>642839</v>
+        <v>642871</v>
       </c>
       <c r="R14" t="n">
-        <v>7037339</v>
+        <v>7037374</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2118,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113714598</v>
+        <v>113712371</v>
       </c>
       <c r="B15" t="n">
-        <v>90153</v>
+        <v>90577</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,25 +2125,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2158,10 +2153,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>642871</v>
+        <v>642825</v>
       </c>
       <c r="R15" t="n">
-        <v>7037374</v>
+        <v>7037328</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2224,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113714594</v>
+        <v>113714592</v>
       </c>
       <c r="B16" t="n">
-        <v>91417</v>
+        <v>56029</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2236,25 +2231,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>642708</v>
+        <v>642734</v>
       </c>
       <c r="R16" t="n">
-        <v>7037261</v>
+        <v>7037340</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2304,7 +2299,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Många</t>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2335,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113714595</v>
+        <v>113714594</v>
       </c>
       <c r="B17" t="n">
-        <v>90577</v>
+        <v>91417</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2347,25 +2342,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2375,10 +2370,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>642825</v>
+        <v>642708</v>
       </c>
       <c r="R17" t="n">
-        <v>7037328</v>
+        <v>7037261</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2411,6 +2406,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Många</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2441,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113714592</v>
+        <v>113712372</v>
       </c>
       <c r="B18" t="n">
-        <v>56029</v>
+        <v>86390</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2453,25 +2453,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>642734</v>
+        <v>642839</v>
       </c>
       <c r="R18" t="n">
-        <v>7037340</v>
+        <v>7037339</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2517,11 +2517,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-10-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>En tupp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,10 +2547,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113712367</v>
+        <v>113714593</v>
       </c>
       <c r="B19" t="n">
-        <v>79265</v>
+        <v>91410</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2568,21 +2563,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2592,10 +2587,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>642802</v>
+        <v>642716</v>
       </c>
       <c r="R19" t="n">
-        <v>7037327</v>
+        <v>7037332</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2628,6 +2623,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Många</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2658,7 +2658,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113712373</v>
+        <v>113714597</v>
       </c>
       <c r="B20" t="n">
         <v>90320</v>

--- a/artfynd/A 2142-2019 artfynd.xlsx
+++ b/artfynd/A 2142-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
